--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T427"/>
+  <dimension ref="A1:T429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28540,6 +28540,138 @@
       <c r="T427" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>387.36</v>
+      </c>
+      <c r="C428" t="n">
+        <v>384.63</v>
+      </c>
+      <c r="D428" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="E428" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="F428" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="G428" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="H428" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="I428" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="J428" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="K428" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="L428" t="n">
+        <v>363.54</v>
+      </c>
+      <c r="M428" t="n">
+        <v>356.33</v>
+      </c>
+      <c r="N428" t="n">
+        <v>360.38</v>
+      </c>
+      <c r="O428" t="n">
+        <v>354.59</v>
+      </c>
+      <c r="P428" t="n">
+        <v>358.94</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="R428" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="S428" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>387.36</v>
+      </c>
+      <c r="C429" t="n">
+        <v>384.63</v>
+      </c>
+      <c r="D429" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="E429" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="F429" t="n">
+        <v>377.86</v>
+      </c>
+      <c r="G429" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="H429" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="I429" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="J429" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="K429" t="n">
+        <v>363.22</v>
+      </c>
+      <c r="L429" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="M429" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="N429" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="O429" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="P429" t="n">
+        <v>360.48</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="R429" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="S429" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B508"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33637,6 +33769,26 @@
       </c>
       <c r="B508" t="n">
         <v>-0.99</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -33805,28 +33957,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.577901057401628</v>
+        <v>-1.563148025644435</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6011406001433093</v>
+        <v>0.5960890645885329</v>
       </c>
       <c r="M2" t="n">
-        <v>7.794508482707146</v>
+        <v>7.828446210783301</v>
       </c>
       <c r="N2" t="n">
-        <v>98.99806437192179</v>
+        <v>99.78820926080381</v>
       </c>
       <c r="O2" t="n">
-        <v>9.949777101620004</v>
+        <v>9.989404850180206</v>
       </c>
       <c r="P2" t="n">
-        <v>412.5209314245968</v>
+        <v>412.3786398965855</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33883,28 +34035,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.279664852250956</v>
+        <v>-1.268922804532125</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5413987023416735</v>
+        <v>0.5377918589559088</v>
       </c>
       <c r="M3" t="n">
-        <v>7.123134891341196</v>
+        <v>7.149255275486953</v>
       </c>
       <c r="N3" t="n">
-        <v>83.79706283554366</v>
+        <v>84.07702620409526</v>
       </c>
       <c r="O3" t="n">
-        <v>9.15407356511535</v>
+        <v>9.169352550976283</v>
       </c>
       <c r="P3" t="n">
-        <v>406.3317613211847</v>
+        <v>406.2287594174839</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33961,28 +34113,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.253806972684638</v>
+        <v>-1.247206982966047</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6396771366693553</v>
+        <v>0.6385361195408746</v>
       </c>
       <c r="M4" t="n">
-        <v>5.778292338579631</v>
+        <v>5.785541547479812</v>
       </c>
       <c r="N4" t="n">
-        <v>53.33688816279454</v>
+        <v>53.33909337485643</v>
       </c>
       <c r="O4" t="n">
-        <v>7.303210811882301</v>
+        <v>7.303361785839206</v>
       </c>
       <c r="P4" t="n">
-        <v>403.1963487403744</v>
+        <v>403.132792452835</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34039,28 +34191,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.453691045191317</v>
+        <v>-1.442390092474808</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6832113998188389</v>
+        <v>0.6793591882495469</v>
       </c>
       <c r="M5" t="n">
-        <v>5.781170365630538</v>
+        <v>5.823639480453308</v>
       </c>
       <c r="N5" t="n">
-        <v>58.64624042976516</v>
+        <v>59.10536628855643</v>
       </c>
       <c r="O5" t="n">
-        <v>7.658083339176008</v>
+        <v>7.688001449567789</v>
       </c>
       <c r="P5" t="n">
-        <v>400.0051099342231</v>
+        <v>399.8956935222235</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34117,28 +34269,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.554102064116908</v>
+        <v>-1.53628546815686</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7092370530267905</v>
+        <v>0.700240693975507</v>
       </c>
       <c r="M6" t="n">
-        <v>5.797295928872054</v>
+        <v>5.878282882134948</v>
       </c>
       <c r="N6" t="n">
-        <v>59.31477957327098</v>
+        <v>60.86562509706289</v>
       </c>
       <c r="O6" t="n">
-        <v>7.701608895112176</v>
+        <v>7.801642461498917</v>
       </c>
       <c r="P6" t="n">
-        <v>399.0682333104739</v>
+        <v>398.8955439537873</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34195,28 +34347,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.487803514820186</v>
+        <v>-1.477515826114612</v>
       </c>
       <c r="J7" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K7" t="n">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6392760485375855</v>
+        <v>0.6365853478858318</v>
       </c>
       <c r="M7" t="n">
-        <v>6.487916731874654</v>
+        <v>6.510053706138473</v>
       </c>
       <c r="N7" t="n">
-        <v>75.15537638882222</v>
+        <v>75.41483299192414</v>
       </c>
       <c r="O7" t="n">
-        <v>8.669220056546161</v>
+        <v>8.684171405029046</v>
       </c>
       <c r="P7" t="n">
-        <v>397.8473863148655</v>
+        <v>397.7483052707532</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34273,28 +34425,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.496379571654013</v>
+        <v>-1.491343131968083</v>
       </c>
       <c r="J8" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K8" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7115866329947287</v>
+        <v>0.7117770875772087</v>
       </c>
       <c r="M8" t="n">
-        <v>5.73000959965213</v>
+        <v>5.724869943865645</v>
       </c>
       <c r="N8" t="n">
-        <v>54.8485091284706</v>
+        <v>54.73943670801749</v>
       </c>
       <c r="O8" t="n">
-        <v>7.405977931945963</v>
+        <v>7.398610457918263</v>
       </c>
       <c r="P8" t="n">
-        <v>397.7276895130386</v>
+        <v>397.6794196354948</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34351,28 +34503,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.335819166740627</v>
+        <v>-1.332698808315173</v>
       </c>
       <c r="J9" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K9" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6453328887113792</v>
+        <v>0.6464177823130176</v>
       </c>
       <c r="M9" t="n">
-        <v>6.056049175332255</v>
+        <v>6.042331235524832</v>
       </c>
       <c r="N9" t="n">
-        <v>59.13680040300108</v>
+        <v>58.91704666079711</v>
       </c>
       <c r="O9" t="n">
-        <v>7.690045539722186</v>
+        <v>7.675744046071176</v>
       </c>
       <c r="P9" t="n">
-        <v>395.3785693568013</v>
+        <v>395.3486342744968</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34429,28 +34581,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.473566061468426</v>
+        <v>-1.465853174154424</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K10" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6468094316892459</v>
+        <v>0.6456767027958372</v>
       </c>
       <c r="M10" t="n">
-        <v>6.419192494832415</v>
+        <v>6.429223221637059</v>
       </c>
       <c r="N10" t="n">
-        <v>71.31203384413597</v>
+        <v>71.32269979183745</v>
       </c>
       <c r="O10" t="n">
-        <v>8.444645276394738</v>
+        <v>8.445276774140529</v>
       </c>
       <c r="P10" t="n">
-        <v>395.6370644906565</v>
+        <v>395.5628540253708</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34507,28 +34659,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.336212118627059</v>
+        <v>-1.330707008451067</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K11" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L11" t="n">
-        <v>0.625520424970279</v>
+        <v>0.6253770610604252</v>
       </c>
       <c r="M11" t="n">
-        <v>6.351986559384816</v>
+        <v>6.351933364795738</v>
       </c>
       <c r="N11" t="n">
-        <v>64.28776106785234</v>
+        <v>64.16224427454904</v>
       </c>
       <c r="O11" t="n">
-        <v>8.017964895648543</v>
+        <v>8.010133848728687</v>
       </c>
       <c r="P11" t="n">
-        <v>392.3202637935387</v>
+        <v>392.267295656717</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34585,28 +34737,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.172331319636859</v>
+        <v>-1.165184940430204</v>
       </c>
       <c r="J12" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K12" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4828050567088074</v>
+        <v>0.4814976926373551</v>
       </c>
       <c r="M12" t="n">
-        <v>7.170250281787068</v>
+        <v>7.16908089945873</v>
       </c>
       <c r="N12" t="n">
-        <v>88.208811159297</v>
+        <v>88.09089067307904</v>
       </c>
       <c r="O12" t="n">
-        <v>9.391954597382645</v>
+        <v>9.385674758539157</v>
       </c>
       <c r="P12" t="n">
-        <v>387.3457827797321</v>
+        <v>387.2766216428329</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34663,28 +34815,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.254364056519579</v>
+        <v>-1.252598442335854</v>
       </c>
       <c r="J13" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K13" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5351170470368867</v>
+        <v>0.5369090677423363</v>
       </c>
       <c r="M13" t="n">
-        <v>6.768774075893254</v>
+        <v>6.743305111465042</v>
       </c>
       <c r="N13" t="n">
-        <v>81.74612674472567</v>
+        <v>81.38841409762433</v>
       </c>
       <c r="O13" t="n">
-        <v>9.041356465969344</v>
+        <v>9.021552754244933</v>
       </c>
       <c r="P13" t="n">
-        <v>389.0915437375985</v>
+        <v>389.0743844044276</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34741,28 +34893,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9800240404056819</v>
+        <v>-0.9780331132694551</v>
       </c>
       <c r="J14" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K14" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3147810815726223</v>
+        <v>0.3161094741785235</v>
       </c>
       <c r="M14" t="n">
-        <v>8.642391474854675</v>
+        <v>8.609814541232005</v>
       </c>
       <c r="N14" t="n">
-        <v>125.2375541228948</v>
+        <v>124.6668802607836</v>
       </c>
       <c r="O14" t="n">
-        <v>11.19095858820391</v>
+        <v>11.16543238127317</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9372101624954</v>
+        <v>383.9179239188036</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34819,28 +34971,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.118809530348314</v>
+        <v>-1.121921864343247</v>
       </c>
       <c r="J15" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K15" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4383058287361454</v>
+        <v>0.442095706167595</v>
       </c>
       <c r="M15" t="n">
-        <v>7.915919960326456</v>
+        <v>7.89451882102796</v>
       </c>
       <c r="N15" t="n">
-        <v>96.60788764621664</v>
+        <v>96.20943644442072</v>
       </c>
       <c r="O15" t="n">
-        <v>9.828931154821293</v>
+        <v>9.808640907099246</v>
       </c>
       <c r="P15" t="n">
-        <v>388.4125524288502</v>
+        <v>388.44251773259</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34897,28 +35049,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8937743860764281</v>
+        <v>-0.8963220282272052</v>
       </c>
       <c r="J16" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K16" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2388502108420111</v>
+        <v>0.2417408773586341</v>
       </c>
       <c r="M16" t="n">
-        <v>8.485267951728932</v>
+        <v>8.461364188004005</v>
       </c>
       <c r="N16" t="n">
-        <v>152.5540385764129</v>
+        <v>151.87988142734</v>
       </c>
       <c r="O16" t="n">
-        <v>12.35127679944114</v>
+        <v>12.32395559174651</v>
       </c>
       <c r="P16" t="n">
-        <v>386.1487294040745</v>
+        <v>386.1732935891825</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34975,28 +35127,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.161420660290196</v>
+        <v>-1.164464125348059</v>
       </c>
       <c r="J17" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K17" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2944925145908764</v>
+        <v>0.2976749397768429</v>
       </c>
       <c r="M17" t="n">
-        <v>8.706339696850389</v>
+        <v>8.679022119644728</v>
       </c>
       <c r="N17" t="n">
-        <v>196.0946683546764</v>
+        <v>195.2311373292656</v>
       </c>
       <c r="O17" t="n">
-        <v>14.00338060450677</v>
+        <v>13.97251363675361</v>
       </c>
       <c r="P17" t="n">
-        <v>398.3959590457579</v>
+        <v>398.4251038726037</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35053,28 +35205,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9602997511011776</v>
+        <v>-0.9608606435666357</v>
       </c>
       <c r="J18" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K18" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3600888882738469</v>
+        <v>0.3627307989930635</v>
       </c>
       <c r="M18" t="n">
-        <v>7.81763989775662</v>
+        <v>7.78596460927192</v>
       </c>
       <c r="N18" t="n">
-        <v>99.20562749565177</v>
+        <v>98.7442606328498</v>
       </c>
       <c r="O18" t="n">
-        <v>9.960202181464579</v>
+        <v>9.937014674078418</v>
       </c>
       <c r="P18" t="n">
-        <v>405.3533264603529</v>
+        <v>405.3587023450881</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35131,28 +35283,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.05248606446583</v>
+        <v>-1.054966585772341</v>
       </c>
       <c r="J19" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K19" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4178363157871118</v>
+        <v>0.4214112295699211</v>
       </c>
       <c r="M19" t="n">
-        <v>7.455118832091125</v>
+        <v>7.431879271556456</v>
       </c>
       <c r="N19" t="n">
-        <v>93.06727517861589</v>
+        <v>92.67042063529306</v>
       </c>
       <c r="O19" t="n">
-        <v>9.647138185939697</v>
+        <v>9.626547700774823</v>
       </c>
       <c r="P19" t="n">
-        <v>404.2605781584898</v>
+        <v>404.2843682201076</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35190,7 +35342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T427"/>
+  <dimension ref="A1:T429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78535,6 +78687,210 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-40.97520701318926,172.10342222903665</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-40.974536597032895,172.10328380438784</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-40.97385891719533,172.1031969093112</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-40.97318759911128,172.10306479263696</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-40.972527645217255,172.10285193447467</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-40.971848892290744,172.10277251420283</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-40.97117274916915,172.10267451393347</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-40.97050635752365,172.1025072245114</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-40.96984328314397,172.10231633303792</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-40.96917373509113,172.10217136024198</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-40.96850751252087,172.1019971535618</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-40.96782805923229,172.10192326016127</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-40.96716646876265,172.101717924453</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-40.96648991480129,172.10162784577136</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-40.96582877536047,172.10141899775817</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-40.96516737051947,172.10121214190568</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-40.964522839559194,172.1008752772121</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>-40.96384688226303,172.10078039586924</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-40.97520701318926,172.10342222903665</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-40.974536597032895,172.10328380438784</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-40.97385891719533,172.1031969093112</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-40.97318759911128,172.10306479263696</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-40.972527645217255,172.10285193447467</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-40.971848892290744,172.10277251420283</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-40.97117274916915,172.10267451393347</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-40.97050635752365,172.1025072245114</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-40.96984328314397,172.10231633303792</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-40.96917373509113,172.10217136024198</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-40.96851014324655,172.10197773400338</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-40.96783296137764,172.10188554489045</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-40.96716616459454,172.1017202670636</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-40.96649243939036,172.1016084023003</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-40.965831117426475,172.10140096001473</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-40.96517100524825,172.10118414853687</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>-40.96452580507911,172.10085243764559</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>-40.96384892010378,172.10076470114723</t>
+        </is>
+      </c>
+      <c r="T429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T429"/>
+  <dimension ref="A1:T432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28672,6 +28672,204 @@
       <c r="T429" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="C430" t="n">
+        <v>386.06</v>
+      </c>
+      <c r="D430" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="E430" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="F430" t="n">
+        <v>377.46</v>
+      </c>
+      <c r="G430" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="H430" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="I430" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="J430" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="K430" t="n">
+        <v>364.08</v>
+      </c>
+      <c r="L430" t="n">
+        <v>365.45</v>
+      </c>
+      <c r="M430" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="N430" t="n">
+        <v>359.87</v>
+      </c>
+      <c r="O430" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="P430" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>366.71</v>
+      </c>
+      <c r="R430" t="n">
+        <v>380.63</v>
+      </c>
+      <c r="S430" t="n">
+        <v>374.28</v>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>386.52</v>
+      </c>
+      <c r="C431" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="D431" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="E431" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="F431" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="G431" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="H431" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="I431" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="J431" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="K431" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="L431" t="n">
+        <v>365.71</v>
+      </c>
+      <c r="M431" t="n">
+        <v>361.66</v>
+      </c>
+      <c r="N431" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="O431" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="P431" t="n">
+        <v>361.48</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="R431" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="S431" t="n">
+        <v>374.73</v>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>386.52</v>
+      </c>
+      <c r="C432" t="n">
+        <v>384.08</v>
+      </c>
+      <c r="D432" t="n">
+        <v>377.79</v>
+      </c>
+      <c r="E432" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="F432" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="G432" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="H432" t="n">
+        <v>362.43</v>
+      </c>
+      <c r="I432" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="J432" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="K432" t="n">
+        <v>361.89</v>
+      </c>
+      <c r="L432" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="M432" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="N432" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="O432" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="P432" t="n">
+        <v>362.95</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="R432" t="n">
+        <v>382.28</v>
+      </c>
+      <c r="S432" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28686,7 +28884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33789,6 +33987,36 @@
       </c>
       <c r="B510" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -33957,28 +34185,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.563148025644435</v>
+        <v>-1.542224735028295</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5960890645885329</v>
+        <v>0.5891872018303228</v>
       </c>
       <c r="M2" t="n">
-        <v>7.828446210783301</v>
+        <v>7.876252128404623</v>
       </c>
       <c r="N2" t="n">
-        <v>99.78820926080381</v>
+        <v>100.8009389484284</v>
       </c>
       <c r="O2" t="n">
-        <v>9.989404850180206</v>
+        <v>10.03996707905103</v>
       </c>
       <c r="P2" t="n">
-        <v>412.3786398965855</v>
+        <v>412.1760267615697</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34035,28 +34263,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.268922804532125</v>
+        <v>-1.252994337148137</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5377918589559088</v>
+        <v>0.5323566166616254</v>
       </c>
       <c r="M3" t="n">
-        <v>7.149255275486953</v>
+        <v>7.188056632055292</v>
       </c>
       <c r="N3" t="n">
-        <v>84.07702620409526</v>
+        <v>84.49762620987468</v>
       </c>
       <c r="O3" t="n">
-        <v>9.169352550976283</v>
+        <v>9.192259037357177</v>
       </c>
       <c r="P3" t="n">
-        <v>406.2287594174839</v>
+        <v>406.0754136635049</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34113,28 +34341,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.247206982966047</v>
+        <v>-1.236737601746067</v>
       </c>
       <c r="J4" t="n">
+        <v>431</v>
+      </c>
+      <c r="K4" t="n">
         <v>428</v>
       </c>
-      <c r="K4" t="n">
-        <v>425</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6385361195408746</v>
+        <v>0.6363205038784298</v>
       </c>
       <c r="M4" t="n">
-        <v>5.785541547479812</v>
+        <v>5.800508411961288</v>
       </c>
       <c r="N4" t="n">
-        <v>53.33909337485643</v>
+        <v>53.39747492756803</v>
       </c>
       <c r="O4" t="n">
-        <v>7.303361785839206</v>
+        <v>7.307357588593022</v>
       </c>
       <c r="P4" t="n">
-        <v>403.132792452835</v>
+        <v>403.0315676052473</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34191,28 +34419,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.442390092474808</v>
+        <v>-1.426057703208022</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6793591882495469</v>
+        <v>0.6739080248781499</v>
       </c>
       <c r="M5" t="n">
-        <v>5.823639480453308</v>
+        <v>5.885493997885748</v>
       </c>
       <c r="N5" t="n">
-        <v>59.10536628855643</v>
+        <v>59.7309420735361</v>
       </c>
       <c r="O5" t="n">
-        <v>7.688001449567789</v>
+        <v>7.728579563770829</v>
       </c>
       <c r="P5" t="n">
-        <v>399.8956935222235</v>
+        <v>399.7369201261566</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34269,28 +34497,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.53628546815686</v>
+        <v>-1.513857872640617</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L6" t="n">
-        <v>0.700240693975507</v>
+        <v>0.6904310683498325</v>
       </c>
       <c r="M6" t="n">
-        <v>5.878282882134948</v>
+        <v>5.972655725087501</v>
       </c>
       <c r="N6" t="n">
-        <v>60.86562509706289</v>
+        <v>62.42133990142745</v>
       </c>
       <c r="O6" t="n">
-        <v>7.801642461498917</v>
+        <v>7.900717682680951</v>
       </c>
       <c r="P6" t="n">
-        <v>398.8955439537873</v>
+        <v>398.6772932249222</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34347,28 +34575,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.477515826114612</v>
+        <v>-1.465386165265135</v>
       </c>
       <c r="J7" t="n">
+        <v>431</v>
+      </c>
+      <c r="K7" t="n">
         <v>428</v>
       </c>
-      <c r="K7" t="n">
-        <v>425</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.6365853478858318</v>
+        <v>0.634460729070317</v>
       </c>
       <c r="M7" t="n">
-        <v>6.510053706138473</v>
+        <v>6.527834776358092</v>
       </c>
       <c r="N7" t="n">
-        <v>75.41483299192414</v>
+        <v>75.49690233203076</v>
       </c>
       <c r="O7" t="n">
-        <v>8.684171405029046</v>
+        <v>8.688895345901615</v>
       </c>
       <c r="P7" t="n">
-        <v>397.7483052707532</v>
+        <v>397.6310300722342</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34425,28 +34653,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.491343131968083</v>
+        <v>-1.484488217108689</v>
       </c>
       <c r="J8" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7117770875772087</v>
+        <v>0.7123008777593158</v>
       </c>
       <c r="M8" t="n">
-        <v>5.724869943865645</v>
+        <v>5.714239868607462</v>
       </c>
       <c r="N8" t="n">
-        <v>54.73943670801749</v>
+        <v>54.55596159976223</v>
       </c>
       <c r="O8" t="n">
-        <v>7.398610457918263</v>
+        <v>7.386200755446756</v>
       </c>
       <c r="P8" t="n">
-        <v>397.6794196354948</v>
+        <v>397.6134668003961</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34503,28 +34731,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.332698808315173</v>
+        <v>-1.328883803307692</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K9" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6464177823130176</v>
+        <v>0.6483892590669689</v>
       </c>
       <c r="M9" t="n">
-        <v>6.042331235524832</v>
+        <v>6.01794031771338</v>
       </c>
       <c r="N9" t="n">
-        <v>58.91704666079711</v>
+        <v>58.56853200278872</v>
       </c>
       <c r="O9" t="n">
-        <v>7.675744046071176</v>
+        <v>7.653008036242267</v>
       </c>
       <c r="P9" t="n">
-        <v>395.3486342744968</v>
+        <v>395.3118942565869</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34581,28 +34809,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.465853174154424</v>
+        <v>-1.458750382600785</v>
       </c>
       <c r="J10" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6456767027958372</v>
+        <v>0.6462178273017488</v>
       </c>
       <c r="M10" t="n">
-        <v>6.429223221637059</v>
+        <v>6.42105391037832</v>
       </c>
       <c r="N10" t="n">
-        <v>71.32269979183745</v>
+        <v>71.06255911165759</v>
       </c>
       <c r="O10" t="n">
-        <v>8.445276774140529</v>
+        <v>8.42986115613167</v>
       </c>
       <c r="P10" t="n">
-        <v>395.5628540253708</v>
+        <v>395.4942592003407</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34659,28 +34887,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.330707008451067</v>
+        <v>-1.323717838651093</v>
       </c>
       <c r="J11" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K11" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6253770610604252</v>
+        <v>0.6257786129136766</v>
       </c>
       <c r="M11" t="n">
-        <v>6.351933364795738</v>
+        <v>6.34480122550324</v>
       </c>
       <c r="N11" t="n">
-        <v>64.16224427454904</v>
+        <v>63.91762042579467</v>
       </c>
       <c r="O11" t="n">
-        <v>8.010133848728687</v>
+        <v>7.994849618710453</v>
       </c>
       <c r="P11" t="n">
-        <v>392.267295656717</v>
+        <v>392.199785711103</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34737,28 +34965,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.165184940430204</v>
+        <v>-1.152794319533029</v>
       </c>
       <c r="J12" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4814976926373551</v>
+        <v>0.4783025457158854</v>
       </c>
       <c r="M12" t="n">
-        <v>7.16908089945873</v>
+        <v>7.176262497495219</v>
       </c>
       <c r="N12" t="n">
-        <v>88.09089067307904</v>
+        <v>88.07270404780876</v>
       </c>
       <c r="O12" t="n">
-        <v>9.385674758539157</v>
+        <v>9.384705858353193</v>
       </c>
       <c r="P12" t="n">
-        <v>387.2766216428329</v>
+        <v>387.1562321267533</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34815,28 +35043,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.252598442335854</v>
+        <v>-1.244651055274492</v>
       </c>
       <c r="J13" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K13" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5369090677423363</v>
+        <v>0.5368059005117521</v>
       </c>
       <c r="M13" t="n">
-        <v>6.743305111465042</v>
+        <v>6.725323782393648</v>
       </c>
       <c r="N13" t="n">
-        <v>81.38841409762433</v>
+        <v>81.06608447276311</v>
       </c>
       <c r="O13" t="n">
-        <v>9.021552754244933</v>
+        <v>9.003670611076524</v>
       </c>
       <c r="P13" t="n">
-        <v>389.0743844044276</v>
+        <v>388.9968929472594</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34893,28 +35121,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9780331132694551</v>
+        <v>-0.977662694267426</v>
       </c>
       <c r="J14" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K14" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3161094741785235</v>
+        <v>0.3192780867478314</v>
       </c>
       <c r="M14" t="n">
-        <v>8.609814541232005</v>
+        <v>8.555285394691422</v>
       </c>
       <c r="N14" t="n">
-        <v>124.6668802607836</v>
+        <v>123.7963578221632</v>
       </c>
       <c r="O14" t="n">
-        <v>11.16543238127317</v>
+        <v>11.12638116469875</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9179239188036</v>
+        <v>383.9143298896004</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34971,28 +35199,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.121921864343247</v>
+        <v>-1.126407164280542</v>
       </c>
       <c r="J15" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K15" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L15" t="n">
-        <v>0.442095706167595</v>
+        <v>0.4476701094906808</v>
       </c>
       <c r="M15" t="n">
-        <v>7.89451882102796</v>
+        <v>7.862187683927893</v>
       </c>
       <c r="N15" t="n">
-        <v>96.20943644442072</v>
+        <v>95.61784232153528</v>
       </c>
       <c r="O15" t="n">
-        <v>9.808640907099246</v>
+        <v>9.778437621702931</v>
       </c>
       <c r="P15" t="n">
-        <v>388.44251773259</v>
+        <v>388.4858953318273</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35049,28 +35277,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8963220282272052</v>
+        <v>-0.897336238723949</v>
       </c>
       <c r="J16" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K16" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2417408773586341</v>
+        <v>0.2449909922301674</v>
       </c>
       <c r="M16" t="n">
-        <v>8.461364188004005</v>
+        <v>8.411099196265127</v>
       </c>
       <c r="N16" t="n">
-        <v>151.87988142734</v>
+        <v>150.8311419742771</v>
       </c>
       <c r="O16" t="n">
-        <v>12.32395559174651</v>
+        <v>12.28133306991864</v>
       </c>
       <c r="P16" t="n">
-        <v>386.1732935891825</v>
+        <v>386.1831043445359</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35127,28 +35355,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.164464125348059</v>
+        <v>-1.163050230617894</v>
       </c>
       <c r="J17" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K17" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2976749397768429</v>
+        <v>0.300360487155147</v>
       </c>
       <c r="M17" t="n">
-        <v>8.679022119644728</v>
+        <v>8.630842728339955</v>
       </c>
       <c r="N17" t="n">
-        <v>195.2311373292656</v>
+        <v>193.8852368221074</v>
       </c>
       <c r="O17" t="n">
-        <v>13.97251363675361</v>
+        <v>13.92426790973613</v>
       </c>
       <c r="P17" t="n">
-        <v>398.4251038726037</v>
+        <v>398.4114856413243</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35205,28 +35433,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9608606435666357</v>
+        <v>-0.9590763468713542</v>
       </c>
       <c r="J18" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K18" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3627307989930635</v>
+        <v>0.3653896509526972</v>
       </c>
       <c r="M18" t="n">
-        <v>7.78596460927192</v>
+        <v>7.739067167085431</v>
       </c>
       <c r="N18" t="n">
-        <v>98.7442606328498</v>
+        <v>98.0669298335625</v>
       </c>
       <c r="O18" t="n">
-        <v>9.937014674078418</v>
+        <v>9.902874826713832</v>
       </c>
       <c r="P18" t="n">
-        <v>405.3587023450881</v>
+        <v>405.3414924373794</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35283,28 +35511,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.054966585772341</v>
+        <v>-1.057027724029663</v>
       </c>
       <c r="J19" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K19" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4214112295699211</v>
+        <v>0.426082207764987</v>
       </c>
       <c r="M19" t="n">
-        <v>7.431879271556456</v>
+        <v>7.389712933337965</v>
       </c>
       <c r="N19" t="n">
-        <v>92.67042063529306</v>
+        <v>92.04348349548266</v>
       </c>
       <c r="O19" t="n">
-        <v>9.626547700774823</v>
+        <v>9.593929512743079</v>
       </c>
       <c r="P19" t="n">
-        <v>404.2843682201076</v>
+        <v>404.3042169502891</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35342,7 +35570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T429"/>
+  <dimension ref="A1:T432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78891,6 +79119,312 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-40.975207046101104,172.10342199533486</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-40.97453895021728,172.1032670948773</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-40.97386066151207,172.10318452336696</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-40.97318682569044,172.1030702844627</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-40.97252698699266,172.1028566083236</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-40.97185025810525,172.10276281606522</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-40.97117516813685,172.1026573378881</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-40.97050713093063,172.102501732905</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-40.969843497063465,172.10231481409784</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-40.96917515024375,172.102161311969</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-40.96851053943989,172.10197480937097</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-40.96783477303691,172.10187160663685</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-40.96716569313387,172.10172389811</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-40.96649315418304,172.10160289722086</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-40.96583126950859,172.10139978873264</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-40.96517283021408,172.10117009328783</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>-40.96452623089699,172.1008491581179</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>-40.9638487984417,172.1007656381456</t>
+        </is>
+      </c>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-40.97520563089202,172.103432044511</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-40.97453569196133,172.10329023112234</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-40.97385941087002,172.10319340385536</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-40.97318746746519,172.1030657274158</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-40.972521145240975,172.10289808872906</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-40.971842589786625,172.10281726584475</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-40.97117034665444,172.10269157313374</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-40.97050431704436,172.10252171300428</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-40.969835137733114,172.10237416959612</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-40.96917011492928,172.10219706512447</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-40.968510951480894,172.1019717677532</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-40.967836173646276,172.10186083084363</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-40.96716163248407,172.10175517195933</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-40.96648892625648,172.1016354591783</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-40.96583263824704,172.10138924719365</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-40.96517587182001,172.1011466678711</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-40.96452664150699,172.1008459957162</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>-40.96384948279078,172.1007603675298</t>
+        </is>
+      </c>
+      <c r="T431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-40.97520563089202,172.103432044511</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-40.97453569196133,172.10329023112234</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-40.97385941087002,172.10319340385536</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-40.97318746746519,172.1030657274158</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-40.972521145240975,172.10289808872906</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-40.971842589786625,172.10281726584475</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-40.97117034665444,172.10269157313374</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-40.97050431704436,172.10252171300428</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-40.969835137733114,172.10237416959612</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-40.969171546539435,172.10218690001219</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-40.96851163293314,172.1019667373853</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-40.9678385181423,172.10184279310187</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-40.96716259061568,172.10174779273677</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-40.96649116188787,172.10161824116534</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-40.96583487385112,172.10137202934578</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-40.965178685301225,172.10112499935877</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>-40.96452874017897,172.1008298323291</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>-40.96385038004807,172.10075345716672</t>
+        </is>
+      </c>
+      <c r="T432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T432"/>
+  <dimension ref="A1:T434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28868,6 +28868,138 @@
         <v>375.32</v>
       </c>
       <c r="T432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>384.49</v>
+      </c>
+      <c r="C433" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="D433" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="E433" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="F433" t="n">
+        <v>374.59</v>
+      </c>
+      <c r="G433" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="H433" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="I433" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="J433" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="K433" t="n">
+        <v>358.17</v>
+      </c>
+      <c r="L433" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="M433" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="N433" t="n">
+        <v>359.38</v>
+      </c>
+      <c r="O433" t="n">
+        <v>357.16</v>
+      </c>
+      <c r="P433" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>372.07</v>
+      </c>
+      <c r="R433" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="S433" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>383.27</v>
+      </c>
+      <c r="C434" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="D434" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="E434" t="n">
+        <v>374.32</v>
+      </c>
+      <c r="F434" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="G434" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="H434" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="I434" t="n">
+        <v>361.07</v>
+      </c>
+      <c r="J434" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="K434" t="n">
+        <v>359.22</v>
+      </c>
+      <c r="L434" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="M434" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="N434" t="n">
+        <v>360.46</v>
+      </c>
+      <c r="O434" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="P434" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="R434" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="S434" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="T434" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28884,7 +29016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34017,6 +34149,26 @@
       </c>
       <c r="B513" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -34185,28 +34337,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.542224735028295</v>
+        <v>-1.531175063195657</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5891872018303228</v>
+        <v>0.5864087446368497</v>
       </c>
       <c r="M2" t="n">
-        <v>7.876252128404623</v>
+        <v>7.894988495339748</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8009389484284</v>
+        <v>101.0655609856117</v>
       </c>
       <c r="O2" t="n">
-        <v>10.03996707905103</v>
+        <v>10.05313687291742</v>
       </c>
       <c r="P2" t="n">
-        <v>412.1760267615697</v>
+        <v>412.068692048575</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34263,28 +34415,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.252994337148137</v>
+        <v>-1.245097918004789</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5323566166616254</v>
+        <v>0.53061713344804</v>
       </c>
       <c r="M3" t="n">
-        <v>7.188056632055292</v>
+        <v>7.199528661863059</v>
       </c>
       <c r="N3" t="n">
-        <v>84.49762620987468</v>
+        <v>84.48425541288078</v>
       </c>
       <c r="O3" t="n">
-        <v>9.192259037357177</v>
+        <v>9.191531722889325</v>
       </c>
       <c r="P3" t="n">
-        <v>406.0754136635049</v>
+        <v>405.9991514535336</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34341,28 +34493,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.236737601746067</v>
+        <v>-1.230456426072745</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6363205038784298</v>
+        <v>0.6352701691116273</v>
       </c>
       <c r="M4" t="n">
-        <v>5.800508411961288</v>
+        <v>5.807371251783749</v>
       </c>
       <c r="N4" t="n">
-        <v>53.39747492756803</v>
+        <v>53.38821730211099</v>
       </c>
       <c r="O4" t="n">
-        <v>7.307357588593022</v>
+        <v>7.306724115642453</v>
       </c>
       <c r="P4" t="n">
-        <v>403.0315676052473</v>
+        <v>402.9706464647866</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34419,28 +34571,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.426057703208022</v>
+        <v>-1.414542908094309</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6739080248781499</v>
+        <v>0.6696463846059515</v>
       </c>
       <c r="M5" t="n">
-        <v>5.885493997885748</v>
+        <v>5.931394900336478</v>
       </c>
       <c r="N5" t="n">
-        <v>59.7309420735361</v>
+        <v>60.24699269580238</v>
       </c>
       <c r="O5" t="n">
-        <v>7.728579563770829</v>
+        <v>7.76189362822001</v>
       </c>
       <c r="P5" t="n">
-        <v>399.7369201261566</v>
+        <v>399.6246334965922</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34497,28 +34649,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.513857872640617</v>
+        <v>-1.500190427500537</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6904310683498325</v>
+        <v>0.6848804069307628</v>
       </c>
       <c r="M6" t="n">
-        <v>5.972655725087501</v>
+        <v>6.026997178027971</v>
       </c>
       <c r="N6" t="n">
-        <v>62.42133990142745</v>
+        <v>63.2483958170067</v>
       </c>
       <c r="O6" t="n">
-        <v>7.900717682680951</v>
+        <v>7.952886005533256</v>
       </c>
       <c r="P6" t="n">
-        <v>398.6772932249222</v>
+        <v>398.5438624286954</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34575,28 +34727,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.465386165265135</v>
+        <v>-1.461011484309712</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>0.634460729070317</v>
+        <v>0.6350750254965958</v>
       </c>
       <c r="M7" t="n">
-        <v>6.527834776358092</v>
+        <v>6.520217082539659</v>
       </c>
       <c r="N7" t="n">
-        <v>75.49690233203076</v>
+        <v>75.26080810333922</v>
       </c>
       <c r="O7" t="n">
-        <v>8.688895345901615</v>
+        <v>8.675298732801034</v>
       </c>
       <c r="P7" t="n">
-        <v>397.6310300722342</v>
+        <v>397.5885907254113</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34653,28 +34805,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.484488217108689</v>
+        <v>-1.481731816583986</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7123008777593158</v>
+        <v>0.7134403766300116</v>
       </c>
       <c r="M8" t="n">
-        <v>5.714239868607462</v>
+        <v>5.699589939768379</v>
       </c>
       <c r="N8" t="n">
-        <v>54.55596159976223</v>
+        <v>54.35010161809988</v>
       </c>
       <c r="O8" t="n">
-        <v>7.386200755446756</v>
+        <v>7.37225214016042</v>
       </c>
       <c r="P8" t="n">
-        <v>397.6134668003961</v>
+        <v>397.5868533684423</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34731,28 +34883,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.328883803307692</v>
+        <v>-1.32834982811184</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6483892590669689</v>
+        <v>0.6505067967312348</v>
       </c>
       <c r="M9" t="n">
-        <v>6.01794031771338</v>
+        <v>5.992586043279535</v>
       </c>
       <c r="N9" t="n">
-        <v>58.56853200278872</v>
+        <v>58.30065675058779</v>
       </c>
       <c r="O9" t="n">
-        <v>7.653008036242267</v>
+        <v>7.635486674115003</v>
       </c>
       <c r="P9" t="n">
-        <v>395.3118942565869</v>
+        <v>395.3067303579979</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34809,28 +34961,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.458750382600785</v>
+        <v>-1.457145575734628</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K10" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6462178273017488</v>
+        <v>0.6479794114423238</v>
       </c>
       <c r="M10" t="n">
-        <v>6.42105391037832</v>
+        <v>6.399611631596009</v>
       </c>
       <c r="N10" t="n">
-        <v>71.06255911165759</v>
+        <v>70.75045106820707</v>
       </c>
       <c r="O10" t="n">
-        <v>8.42986115613167</v>
+        <v>8.411328733809366</v>
       </c>
       <c r="P10" t="n">
-        <v>395.4942592003407</v>
+        <v>395.4787015601343</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34887,28 +35039,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.323717838651093</v>
+        <v>-1.32229429840889</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K11" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6257786129136766</v>
+        <v>0.6276007208484055</v>
       </c>
       <c r="M11" t="n">
-        <v>6.34480122550324</v>
+        <v>6.32291607361093</v>
       </c>
       <c r="N11" t="n">
-        <v>63.91762042579467</v>
+        <v>63.63530351823309</v>
       </c>
       <c r="O11" t="n">
-        <v>7.994849618710453</v>
+        <v>7.977173905477621</v>
       </c>
       <c r="P11" t="n">
-        <v>392.199785711103</v>
+        <v>392.1859847393301</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34965,28 +35117,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.152794319533029</v>
+        <v>-1.146085881699647</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K12" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4783025457158854</v>
+        <v>0.4771559268016892</v>
       </c>
       <c r="M12" t="n">
-        <v>7.176262497495219</v>
+        <v>7.175041363358881</v>
       </c>
       <c r="N12" t="n">
-        <v>88.07270404780876</v>
+        <v>87.93208643125109</v>
       </c>
       <c r="O12" t="n">
-        <v>9.384705858353193</v>
+        <v>9.377211015608591</v>
       </c>
       <c r="P12" t="n">
-        <v>387.1562321267533</v>
+        <v>387.090843427667</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35043,28 +35195,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.244651055274492</v>
+        <v>-1.236525798125169</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K13" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5368059005117521</v>
+        <v>0.5348645028315226</v>
       </c>
       <c r="M13" t="n">
-        <v>6.725323782393648</v>
+        <v>6.724341142198725</v>
       </c>
       <c r="N13" t="n">
-        <v>81.06608447276311</v>
+        <v>81.07962287686071</v>
       </c>
       <c r="O13" t="n">
-        <v>9.003670611076524</v>
+        <v>9.004422406621133</v>
       </c>
       <c r="P13" t="n">
-        <v>388.9968929472594</v>
+        <v>388.917425003668</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35121,28 +35273,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.977662694267426</v>
+        <v>-0.9759349120477906</v>
       </c>
       <c r="J14" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K14" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3192780867478314</v>
+        <v>0.3206870223654118</v>
       </c>
       <c r="M14" t="n">
-        <v>8.555285394691422</v>
+        <v>8.522564497334914</v>
       </c>
       <c r="N14" t="n">
-        <v>123.7963578221632</v>
+        <v>123.2358184484051</v>
       </c>
       <c r="O14" t="n">
-        <v>11.12638116469875</v>
+        <v>11.10116293225197</v>
       </c>
       <c r="P14" t="n">
-        <v>383.9143298896004</v>
+        <v>383.8974652559718</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35199,28 +35351,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.126407164280542</v>
+        <v>-1.126821811787494</v>
       </c>
       <c r="J15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K15" t="n">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4476701094906808</v>
+        <v>0.4503626889118721</v>
       </c>
       <c r="M15" t="n">
-        <v>7.862187683927893</v>
+        <v>7.829933064948132</v>
       </c>
       <c r="N15" t="n">
-        <v>95.61784232153528</v>
+        <v>95.17549410004642</v>
       </c>
       <c r="O15" t="n">
-        <v>9.778437621702931</v>
+        <v>9.755792848356633</v>
       </c>
       <c r="P15" t="n">
-        <v>388.4858953318273</v>
+        <v>388.4899084097819</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35277,28 +35429,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.897336238723949</v>
+        <v>-0.8957673964266066</v>
       </c>
       <c r="J16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K16" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2449909922301674</v>
+        <v>0.2462055139773451</v>
       </c>
       <c r="M16" t="n">
-        <v>8.411099196265127</v>
+        <v>8.378900727364181</v>
       </c>
       <c r="N16" t="n">
-        <v>150.8311419742771</v>
+        <v>150.1510140850963</v>
       </c>
       <c r="O16" t="n">
-        <v>12.28133306991864</v>
+        <v>12.25361228720316</v>
       </c>
       <c r="P16" t="n">
-        <v>386.1831043445359</v>
+        <v>386.1678560000353</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35355,28 +35507,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.163050230617894</v>
+        <v>-1.158885507023331</v>
       </c>
       <c r="J17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K17" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L17" t="n">
-        <v>0.300360487155147</v>
+        <v>0.3008642673617626</v>
       </c>
       <c r="M17" t="n">
-        <v>8.630842728339955</v>
+        <v>8.615803861287485</v>
       </c>
       <c r="N17" t="n">
-        <v>193.8852368221074</v>
+        <v>193.0872113610806</v>
       </c>
       <c r="O17" t="n">
-        <v>13.92426790973613</v>
+        <v>13.89558244051254</v>
       </c>
       <c r="P17" t="n">
-        <v>398.4114856413243</v>
+        <v>398.371291915971</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35433,28 +35585,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9590763468713542</v>
+        <v>-0.9579142216451818</v>
       </c>
       <c r="J18" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K18" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3653896509526972</v>
+        <v>0.3671537492812333</v>
       </c>
       <c r="M18" t="n">
-        <v>7.739067167085431</v>
+        <v>7.70801536902466</v>
       </c>
       <c r="N18" t="n">
-        <v>98.0669298335625</v>
+        <v>97.6185837335595</v>
       </c>
       <c r="O18" t="n">
-        <v>9.902874826713832</v>
+        <v>9.880211725138258</v>
       </c>
       <c r="P18" t="n">
-        <v>405.3414924373794</v>
+        <v>405.3302489321477</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35511,28 +35663,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.057027724029663</v>
+        <v>-1.059783905284297</v>
       </c>
       <c r="J19" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K19" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L19" t="n">
-        <v>0.426082207764987</v>
+        <v>0.4297172154734676</v>
       </c>
       <c r="M19" t="n">
-        <v>7.389712933337965</v>
+        <v>7.368232428446405</v>
       </c>
       <c r="N19" t="n">
-        <v>92.04348349548266</v>
+        <v>91.66504828912898</v>
       </c>
       <c r="O19" t="n">
-        <v>9.593929512743079</v>
+        <v>9.574186560179877</v>
       </c>
       <c r="P19" t="n">
-        <v>404.3042169502891</v>
+        <v>404.3308454117046</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35570,7 +35722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T432"/>
+  <dimension ref="A1:T434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79425,6 +79577,210 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-40.97520229033686,172.10345576523915</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-40.974532861553385,172.10331032927283</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-40.973859657707315,172.10319165112742</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-40.97319005101817,172.10304738238017</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-40.97252226422556,172.10289014318715</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-40.97183832777003,172.10284752869978</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-40.97116797704842,172.10270839864523</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-40.970500762656705,172.10254695102208</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-40.96983127070965,172.10240162735124</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-40.96916542516556,172.1022303646273</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-40.96850806719222,172.1019930590767</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-40.96784127368272,172.1018215928973</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-40.967164947921624,172.10172963750585</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-40.96649382335042,172.1015977435294</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-40.96583542134561,172.1013678127298</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-40.965180981707185,172.10110731316632</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>-40.96452658067589,172.10084646422015</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>-40.96384633478305,172.10078461236154</t>
+        </is>
+      </c>
+      <c r="T433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-40.9752002827102,172.10347002104507</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-40.9745313476128,172.1033210794457</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-40.97385789693398,172.10320415391982</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-40.973187763668875,172.1030636241634</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-40.97252050347016,172.10290264573092</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-40.97183859106086,172.10284565917988</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-40.97116924412972,172.1026994016705</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-40.970502144919216,172.1025371362377</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-40.96983298207403,172.10238947583446</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-40.96916715297437,172.10221809638995</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-40.968509081448026,172.1019855720181</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-40.96784179129762,172.10181761053823</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-40.96716659042986,172.10171698740874</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-40.966496712934216,172.10157548895143</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-40.96583799152595,172.10134801805938</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-40.96518177252185,172.10110122255674</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>-40.964527660427734,172.10083814827476</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>-40.963847581820545,172.10077500812892</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T434"/>
+  <dimension ref="A1:T439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29000,6 +29000,336 @@
         <v>373.48</v>
       </c>
       <c r="T434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="C435" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="D435" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="E435" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="F435" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="G435" t="n">
+        <v>365.87</v>
+      </c>
+      <c r="H435" t="n">
+        <v>363.41</v>
+      </c>
+      <c r="I435" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="J435" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="K435" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="L435" t="n">
+        <v>366.18</v>
+      </c>
+      <c r="M435" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="N435" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="O435" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="P435" t="n">
+        <v>368.13</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="R435" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="S435" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="C436" t="n">
+        <v>381.03</v>
+      </c>
+      <c r="D436" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="E436" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="F436" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="G436" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="H436" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="I436" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="J436" t="n">
+        <v>363.83</v>
+      </c>
+      <c r="K436" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="L436" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="M436" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="N436" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="O436" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="P436" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>382.06</v>
+      </c>
+      <c r="R436" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="S436" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:18:45+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="C437" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="D437" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="E437" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="F437" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="G437" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="H437" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="I437" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="J437" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="K437" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="L437" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="M437" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="N437" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="O437" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="P437" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>381.95</v>
+      </c>
+      <c r="R437" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="S437" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="C438" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="D438" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="E438" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="F438" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="G438" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="H438" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="I438" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="J438" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="K438" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="L438" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="M438" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="N438" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="O438" t="n">
+        <v>364.42</v>
+      </c>
+      <c r="P438" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="R438" t="n">
+        <v>390.14</v>
+      </c>
+      <c r="S438" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="C439" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="D439" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="E439" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="F439" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="G439" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="H439" t="n">
+        <v>363.33</v>
+      </c>
+      <c r="I439" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="J439" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="K439" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="L439" t="n">
+        <v>373.62</v>
+      </c>
+      <c r="M439" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="N439" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="O439" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="P439" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>383.15</v>
+      </c>
+      <c r="R439" t="n">
+        <v>391.38</v>
+      </c>
+      <c r="S439" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="T439" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29016,7 +29346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34169,6 +34499,56 @@
       </c>
       <c r="B515" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -34337,28 +34717,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.531175063195657</v>
+        <v>-1.512599557675235</v>
       </c>
       <c r="J2" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5864087446368497</v>
+        <v>0.5842665786698098</v>
       </c>
       <c r="M2" t="n">
-        <v>7.894988495339748</v>
+        <v>7.896404028758935</v>
       </c>
       <c r="N2" t="n">
-        <v>101.0655609856117</v>
+        <v>100.8548832494859</v>
       </c>
       <c r="O2" t="n">
-        <v>10.05313687291742</v>
+        <v>10.04265319771055</v>
       </c>
       <c r="P2" t="n">
-        <v>412.068692048575</v>
+        <v>411.8874934891779</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34415,28 +34795,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.245097918004789</v>
+        <v>-1.230317539011656</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K3" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.53061713344804</v>
+        <v>0.5292260036714704</v>
       </c>
       <c r="M3" t="n">
-        <v>7.199528661863059</v>
+        <v>7.200729987030276</v>
       </c>
       <c r="N3" t="n">
-        <v>84.48425541288078</v>
+        <v>84.07242592921509</v>
       </c>
       <c r="O3" t="n">
-        <v>9.191531722889325</v>
+        <v>9.169101696961109</v>
       </c>
       <c r="P3" t="n">
-        <v>405.9991514535336</v>
+        <v>405.8557764687185</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34493,28 +34873,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.230456426072745</v>
+        <v>-1.218642252892956</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K4" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6352701691116273</v>
+        <v>0.6350144829570363</v>
       </c>
       <c r="M4" t="n">
-        <v>5.807371251783749</v>
+        <v>5.805029750567601</v>
       </c>
       <c r="N4" t="n">
-        <v>53.38821730211099</v>
+        <v>53.13027172450904</v>
       </c>
       <c r="O4" t="n">
-        <v>7.306724115642453</v>
+        <v>7.289051496903355</v>
       </c>
       <c r="P4" t="n">
-        <v>402.9706464647866</v>
+        <v>402.8555503443006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34571,28 +34951,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.414542908094309</v>
+        <v>-1.393855979298035</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K5" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6696463846059515</v>
+        <v>0.6647096406060136</v>
       </c>
       <c r="M5" t="n">
-        <v>5.931394900336478</v>
+        <v>5.993941284494958</v>
       </c>
       <c r="N5" t="n">
-        <v>60.24699269580238</v>
+        <v>60.61882214441223</v>
       </c>
       <c r="O5" t="n">
-        <v>7.76189362822001</v>
+        <v>7.785809023114568</v>
       </c>
       <c r="P5" t="n">
-        <v>399.6246334965922</v>
+        <v>399.4220124423691</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34649,28 +35029,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.500190427500537</v>
+        <v>-1.471526108083395</v>
       </c>
       <c r="J6" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6848804069307628</v>
+        <v>0.6749193759784307</v>
       </c>
       <c r="M6" t="n">
-        <v>6.026997178027971</v>
+        <v>6.13011271989665</v>
       </c>
       <c r="N6" t="n">
-        <v>63.2483958170067</v>
+        <v>64.55804961617046</v>
       </c>
       <c r="O6" t="n">
-        <v>7.952886005533256</v>
+        <v>8.034802400567823</v>
       </c>
       <c r="P6" t="n">
-        <v>398.5438624286954</v>
+        <v>398.2627783588255</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34727,28 +35107,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.461011484309712</v>
+        <v>-1.443700383524354</v>
       </c>
       <c r="J7" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K7" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6350750254965958</v>
+        <v>0.6330352588188189</v>
       </c>
       <c r="M7" t="n">
-        <v>6.520217082539659</v>
+        <v>6.534581847733358</v>
       </c>
       <c r="N7" t="n">
-        <v>75.26080810333922</v>
+        <v>75.13721118487574</v>
       </c>
       <c r="O7" t="n">
-        <v>8.675298732801034</v>
+        <v>8.668172309366938</v>
       </c>
       <c r="P7" t="n">
-        <v>397.5885907254113</v>
+        <v>397.4198860320051</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34805,28 +35185,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.481731816583986</v>
+        <v>-1.468957208348002</v>
       </c>
       <c r="J8" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K8" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7134403766300116</v>
+        <v>0.7134134341341507</v>
       </c>
       <c r="M8" t="n">
-        <v>5.699589939768379</v>
+        <v>5.688943562473906</v>
       </c>
       <c r="N8" t="n">
-        <v>54.35010161809988</v>
+        <v>54.1458740324535</v>
       </c>
       <c r="O8" t="n">
-        <v>7.37225214016042</v>
+        <v>7.358388005022126</v>
       </c>
       <c r="P8" t="n">
-        <v>397.5868533684423</v>
+        <v>397.4629718017792</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34883,28 +35263,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.32834982811184</v>
+        <v>-1.322303663254639</v>
       </c>
       <c r="J9" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K9" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6505067967312348</v>
+        <v>0.6537103956774319</v>
       </c>
       <c r="M9" t="n">
-        <v>5.992586043279535</v>
+        <v>5.951333952869497</v>
       </c>
       <c r="N9" t="n">
-        <v>58.30065675058779</v>
+        <v>57.7331542468695</v>
       </c>
       <c r="O9" t="n">
-        <v>7.635486674115003</v>
+        <v>7.598233626762835</v>
       </c>
       <c r="P9" t="n">
-        <v>395.3067303579979</v>
+        <v>395.2480423037872</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34961,28 +35341,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.457145575734628</v>
+        <v>-1.44269059793371</v>
       </c>
       <c r="J10" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K10" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6479794114423238</v>
+        <v>0.6473528324248062</v>
       </c>
       <c r="M10" t="n">
-        <v>6.399611631596009</v>
+        <v>6.40083713893592</v>
       </c>
       <c r="N10" t="n">
-        <v>70.75045106820707</v>
+        <v>70.48584750683463</v>
       </c>
       <c r="O10" t="n">
-        <v>8.411328733809366</v>
+        <v>8.395585000870078</v>
       </c>
       <c r="P10" t="n">
-        <v>395.4787015601343</v>
+        <v>395.3379370568506</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35039,28 +35419,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.32229429840889</v>
+        <v>-1.301382961477539</v>
       </c>
       <c r="J11" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K11" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6276007208484055</v>
+        <v>0.6216780675944913</v>
       </c>
       <c r="M11" t="n">
-        <v>6.32291607361093</v>
+        <v>6.360181482614475</v>
       </c>
       <c r="N11" t="n">
-        <v>63.63530351823309</v>
+        <v>64.0711297152459</v>
       </c>
       <c r="O11" t="n">
-        <v>7.977173905477621</v>
+        <v>8.00444437267484</v>
       </c>
       <c r="P11" t="n">
-        <v>392.1859847393301</v>
+        <v>391.9823340094139</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35117,28 +35497,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.146085881699647</v>
+        <v>-1.115743400316617</v>
       </c>
       <c r="J12" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K12" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4771559268016892</v>
+        <v>0.4634152926591653</v>
       </c>
       <c r="M12" t="n">
-        <v>7.175041363358881</v>
+        <v>7.235387548817465</v>
       </c>
       <c r="N12" t="n">
-        <v>87.93208643125109</v>
+        <v>89.24835860016567</v>
       </c>
       <c r="O12" t="n">
-        <v>9.377211015608591</v>
+        <v>9.447134941354742</v>
       </c>
       <c r="P12" t="n">
-        <v>387.090843427667</v>
+        <v>386.7936885704738</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35195,28 +35575,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.236525798125169</v>
+        <v>-1.202312173712573</v>
       </c>
       <c r="J13" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K13" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5348645028315226</v>
+        <v>0.5182092634564798</v>
       </c>
       <c r="M13" t="n">
-        <v>6.724341142198725</v>
+        <v>6.785772915558724</v>
       </c>
       <c r="N13" t="n">
-        <v>81.07962287686071</v>
+        <v>83.04989202364125</v>
       </c>
       <c r="O13" t="n">
-        <v>9.004422406621133</v>
+        <v>9.113171348309065</v>
       </c>
       <c r="P13" t="n">
-        <v>388.917425003668</v>
+        <v>388.5812354170237</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35273,28 +35653,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9759349120477906</v>
+        <v>-0.9574571972696908</v>
       </c>
       <c r="J14" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K14" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3206870223654118</v>
+        <v>0.316275399065738</v>
       </c>
       <c r="M14" t="n">
-        <v>8.522564497334914</v>
+        <v>8.501185573045507</v>
       </c>
       <c r="N14" t="n">
-        <v>123.2358184484051</v>
+        <v>122.6755416222991</v>
       </c>
       <c r="O14" t="n">
-        <v>11.10116293225197</v>
+        <v>11.07589913380846</v>
       </c>
       <c r="P14" t="n">
-        <v>383.8974652559718</v>
+        <v>383.716300542425</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35351,28 +35731,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.126821811787494</v>
+        <v>-1.113765776968873</v>
       </c>
       <c r="J15" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K15" t="n">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4503626889118721</v>
+        <v>0.4496279818021095</v>
       </c>
       <c r="M15" t="n">
-        <v>7.829933064948132</v>
+        <v>7.809775505231473</v>
       </c>
       <c r="N15" t="n">
-        <v>95.17549410004642</v>
+        <v>94.52032604422961</v>
       </c>
       <c r="O15" t="n">
-        <v>9.755792848356633</v>
+        <v>9.722156450306157</v>
       </c>
       <c r="P15" t="n">
-        <v>388.4899084097819</v>
+        <v>388.3626398791878</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35429,28 +35809,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8957673964266066</v>
+        <v>-0.8734099440887821</v>
       </c>
       <c r="J16" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K16" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2462055139773451</v>
+        <v>0.2399107510726198</v>
       </c>
       <c r="M16" t="n">
-        <v>8.378900727364181</v>
+        <v>8.377800187502693</v>
       </c>
       <c r="N16" t="n">
-        <v>150.1510140850963</v>
+        <v>149.7256618992632</v>
       </c>
       <c r="O16" t="n">
-        <v>12.25361228720316</v>
+        <v>12.23624378227498</v>
       </c>
       <c r="P16" t="n">
-        <v>386.1678560000353</v>
+        <v>385.9496199118446</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35507,28 +35887,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.158885507023331</v>
+        <v>-1.13007866346054</v>
       </c>
       <c r="J17" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K17" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3008642673617626</v>
+        <v>0.2932237015272759</v>
       </c>
       <c r="M17" t="n">
-        <v>8.615803861287485</v>
+        <v>8.689014800001479</v>
       </c>
       <c r="N17" t="n">
-        <v>193.0872113610806</v>
+        <v>192.9963285814445</v>
       </c>
       <c r="O17" t="n">
-        <v>13.89558244051254</v>
+        <v>13.8923118515762</v>
       </c>
       <c r="P17" t="n">
-        <v>398.371291915971</v>
+        <v>398.0919523008319</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35585,28 +35965,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9579142216451818</v>
+        <v>-0.9372548857688155</v>
       </c>
       <c r="J18" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K18" t="n">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3671537492812333</v>
+        <v>0.3601350885431766</v>
       </c>
       <c r="M18" t="n">
-        <v>7.70801536902466</v>
+        <v>7.708582418185054</v>
       </c>
       <c r="N18" t="n">
-        <v>97.6185837335595</v>
+        <v>97.61823557937376</v>
       </c>
       <c r="O18" t="n">
-        <v>9.880211725138258</v>
+        <v>9.880194106361158</v>
       </c>
       <c r="P18" t="n">
-        <v>405.3302489321477</v>
+        <v>405.1294546150912</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35663,28 +36043,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.059783905284297</v>
+        <v>-1.049977546381093</v>
       </c>
       <c r="J19" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K19" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4297172154734676</v>
+        <v>0.4305157691522268</v>
       </c>
       <c r="M19" t="n">
-        <v>7.368232428446405</v>
+        <v>7.342331781648196</v>
       </c>
       <c r="N19" t="n">
-        <v>91.66504828912898</v>
+        <v>90.89949779144659</v>
       </c>
       <c r="O19" t="n">
-        <v>9.574186560179877</v>
+        <v>9.534122811850422</v>
       </c>
       <c r="P19" t="n">
-        <v>404.3308454117046</v>
+        <v>404.2356070843259</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35722,7 +36102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T434"/>
+  <dimension ref="A1:T439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79781,6 +80161,516 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-40.975199245984264,172.10347738264946</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-40.9745312488775,172.1033217805439</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-40.97385732097978,172.10320824361813</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-40.97318600290201,172.10307612683033</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-40.97252111232966,172.10289832242148</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-40.97184196447194,172.102821705955</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-40.97117195930158,172.1026801224378</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-40.970503856290705,172.10252498459934</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-40.96983510482229,172.10237440327916</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-40.969170970604424,172.10219098942522</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-40.96851169632403,172.10196626944412</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-40.967845460269764,172.10178938263846</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-40.96717092481992,172.1016836052051</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-40.966500743135946,172.10154444966852</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-40.96584275167342,172.10131135692043</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-40.965187521126424,172.10105694850589</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>-40.964532785438806,172.10079867681202</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>-40.963852767662935,172.10073506857256</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-40.97520026625424,172.10347013789593</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-40.97453067292156,172.1033258702834</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-40.97385840706471,172.10320053161553</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-40.973185673786574,172.10307846377734</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-40.972520684482454,172.10290136042272</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-40.97184507458798,172.102799622248</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-40.9711764516697,172.10264822406762</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-40.970507509406296,172.1024990455231</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-40.96984071610854,172.10233456031835</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-40.96917962606948,172.10212953138196</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-40.96851870100616,172.10191456193567</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-40.96785358983478,172.10172683616105</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-40.9671766735749,172.10163932985486</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-40.96650655269498,172.101499706243</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-40.96585032530245,172.10125302704668</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-40.96519617441696,172.10099030316144</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>-40.96454154507025,172.10073121222112</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>-40.96385988486679,172.10068025415697</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:18:45+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-40.97519713961902,172.10349233955924</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-40.974527184271,172.10335064241852</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-40.97385615261511,172.10321653986304</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-40.973183007949665,172.10309739304734</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-40.97251808448622,172.1029198221218</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-40.97184352775832,172.10281060567922</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-40.97117388460329,172.10266645170825</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-40.97050522209587,172.10251528665677</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-40.96984017308145,172.10233841608903</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-40.96918137032272,172.10211714629912</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-40.96852007975307,172.10190438421216</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-40.96785365073026,172.10172636764807</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-40.96717711461623,172.10163593306842</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-40.9665057922825,172.10150556271276</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-40.96585061425558,172.1012508016095</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-40.96519600713052,172.1009915915602</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-40.96454154507025,172.10073121222112</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>-40.96385988486679,172.10068025415697</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-40.97518902680337,172.10354994702357</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-40.974527184271,172.10335064241852</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-40.97385424373634,172.10323009429078</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-40.97318106616526,172.1031111810332</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-40.97251510600585,172.10294097128167</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-40.97184352775832,172.10281060567922</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-40.97117182765695,172.1026810571885</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-40.97050408666754,172.1025233488018</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-40.969842345189065,172.10232299300594</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-40.969183180395405,172.102104293854</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-40.96852115739368,172.10189642920963</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-40.96785282864099,172.10173269257342</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-40.96717711461623,172.10163593306842</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-40.96650486457885,172.10151270760565</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-40.96585218068496,172.10123873739693</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-40.96519623524839,172.1009898346528</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>-40.96454069344116,172.10073777127934</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>-40.96385980882843,172.10068083978115</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-40.97518902680337,172.10354994702357</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-40.974527184271,172.10335064241852</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-40.97385424373634,172.10323009429078</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-40.97318106616526,172.1031111810332</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-40.97251510600585,172.10294097128167</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-40.97184352775832,172.10281060567922</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-40.97117182765695,172.1026810571885</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-40.97050408666754,172.1025233488018</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-40.969842345189065,172.10232299300594</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-40.969183180395405,172.102104293854</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-40.968523486997285,172.101879232365</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-40.96785369640188,172.1017260162633</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-40.96717737315767,172.10163394184877</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-40.96650763248022,172.10149139005577</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-40.96585357982468,172.101227961595</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>-40.965197832072775,172.10097753630095</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>-40.964542579190784,172.10072324765025</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>-40.96386072128861,172.10067381229115</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T439"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29330,6 +29330,204 @@
         <v>382.12</v>
       </c>
       <c r="T439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="C440" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="D440" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="E440" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="F440" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="G440" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="H440" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="I440" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="J440" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="K440" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="L440" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="M440" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="N440" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="O440" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="P440" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="R440" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="S440" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="C441" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="D441" t="n">
+        <v>375.38</v>
+      </c>
+      <c r="E441" t="n">
+        <v>370.25</v>
+      </c>
+      <c r="F441" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="G441" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="H441" t="n">
+        <v>364.11</v>
+      </c>
+      <c r="I441" t="n">
+        <v>363.21</v>
+      </c>
+      <c r="J441" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="K441" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="L441" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="M441" t="n">
+        <v>373.17</v>
+      </c>
+      <c r="N441" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="O441" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="P441" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>383.97</v>
+      </c>
+      <c r="R441" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="S441" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="C442" t="n">
+        <v>376.18</v>
+      </c>
+      <c r="D442" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="E442" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="F442" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="G442" t="n">
+        <v>366.79</v>
+      </c>
+      <c r="H442" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="I442" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="J442" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="K442" t="n">
+        <v>372.34</v>
+      </c>
+      <c r="L442" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="M442" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="N442" t="n">
+        <v>367.94</v>
+      </c>
+      <c r="O442" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="P442" t="n">
+        <v>375.61</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="R442" t="n">
+        <v>392.63</v>
+      </c>
+      <c r="S442" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="T442" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29346,7 +29544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34549,6 +34747,46 @@
       </c>
       <c r="B520" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -34717,28 +34955,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.512599557675235</v>
+        <v>-1.507784085173973</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5842665786698098</v>
+        <v>0.5859872302884308</v>
       </c>
       <c r="M2" t="n">
-        <v>7.896404028758935</v>
+        <v>7.866338808770673</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8548832494859</v>
+        <v>100.2815720158498</v>
       </c>
       <c r="O2" t="n">
-        <v>10.04265319771055</v>
+        <v>10.01406870437036</v>
       </c>
       <c r="P2" t="n">
-        <v>411.8874934891779</v>
+        <v>411.8403816067302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34795,28 +35033,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.230317539011656</v>
+        <v>-1.223810631281719</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5292260036714704</v>
+        <v>0.5296277397333835</v>
       </c>
       <c r="M3" t="n">
-        <v>7.200729987030276</v>
+        <v>7.188298970677899</v>
       </c>
       <c r="N3" t="n">
-        <v>84.07242592921509</v>
+        <v>83.69467242559725</v>
       </c>
       <c r="O3" t="n">
-        <v>9.169101696961109</v>
+        <v>9.148479241141516</v>
       </c>
       <c r="P3" t="n">
-        <v>405.8557764687185</v>
+        <v>405.7924690724522</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34873,28 +35111,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.218642252892956</v>
+        <v>-1.213209416094739</v>
       </c>
       <c r="J4" t="n">
+        <v>441</v>
+      </c>
+      <c r="K4" t="n">
         <v>438</v>
       </c>
-      <c r="K4" t="n">
-        <v>435</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6350144829570363</v>
+        <v>0.6357308852924384</v>
       </c>
       <c r="M4" t="n">
-        <v>5.805029750567601</v>
+        <v>5.794757720451288</v>
       </c>
       <c r="N4" t="n">
-        <v>53.13027172450904</v>
+        <v>52.89958463144672</v>
       </c>
       <c r="O4" t="n">
-        <v>7.289051496903355</v>
+        <v>7.273210063750855</v>
       </c>
       <c r="P4" t="n">
-        <v>402.8555503443006</v>
+        <v>402.8024630008031</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34951,28 +35189,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.393855979298035</v>
+        <v>-1.384311315993423</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6647096406060136</v>
+        <v>0.6634595256732159</v>
       </c>
       <c r="M5" t="n">
-        <v>5.993941284494958</v>
+        <v>6.012559521503573</v>
       </c>
       <c r="N5" t="n">
-        <v>60.61882214441223</v>
+        <v>60.59206886830842</v>
       </c>
       <c r="O5" t="n">
-        <v>7.785809023114568</v>
+        <v>7.784090754115629</v>
       </c>
       <c r="P5" t="n">
-        <v>399.4220124423691</v>
+        <v>399.3282295688964</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35029,28 +35267,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.471526108083395</v>
+        <v>-1.461007929357957</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6749193759784307</v>
+        <v>0.6729669464565554</v>
       </c>
       <c r="M6" t="n">
-        <v>6.13011271989665</v>
+        <v>6.153063195109411</v>
       </c>
       <c r="N6" t="n">
-        <v>64.55804961617046</v>
+        <v>64.69951065087035</v>
       </c>
       <c r="O6" t="n">
-        <v>8.034802400567823</v>
+        <v>8.043600602396314</v>
       </c>
       <c r="P6" t="n">
-        <v>398.2627783588255</v>
+        <v>398.1593647121544</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35107,28 +35345,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.443700383524354</v>
+        <v>-1.432988012196715</v>
       </c>
       <c r="J7" t="n">
+        <v>441</v>
+      </c>
+      <c r="K7" t="n">
         <v>438</v>
       </c>
-      <c r="K7" t="n">
-        <v>435</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.6330352588188189</v>
+        <v>0.6314379283705958</v>
       </c>
       <c r="M7" t="n">
-        <v>6.534581847733358</v>
+        <v>6.545852121187799</v>
       </c>
       <c r="N7" t="n">
-        <v>75.13721118487574</v>
+        <v>75.1133907973058</v>
       </c>
       <c r="O7" t="n">
-        <v>8.668172309366938</v>
+        <v>8.66679818602613</v>
       </c>
       <c r="P7" t="n">
-        <v>397.4198860320051</v>
+        <v>397.3151744519298</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35185,28 +35423,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.468957208348002</v>
+        <v>-1.461675678353924</v>
       </c>
       <c r="J8" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K8" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7134134341341507</v>
+        <v>0.7134952359665163</v>
       </c>
       <c r="M8" t="n">
-        <v>5.688943562473906</v>
+        <v>5.681980314094001</v>
       </c>
       <c r="N8" t="n">
-        <v>54.1458740324535</v>
+        <v>54.00425020413695</v>
       </c>
       <c r="O8" t="n">
-        <v>7.358388005022126</v>
+        <v>7.348758412421581</v>
       </c>
       <c r="P8" t="n">
-        <v>397.4629718017792</v>
+        <v>397.3921371513079</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35263,28 +35501,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.322303663254639</v>
+        <v>-1.307856256843581</v>
       </c>
       <c r="J9" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6537103956774319</v>
+        <v>0.6448822725871937</v>
       </c>
       <c r="M9" t="n">
-        <v>5.951333952869497</v>
+        <v>5.975761990487921</v>
       </c>
       <c r="N9" t="n">
-        <v>57.7331542468695</v>
+        <v>59.16765751618538</v>
       </c>
       <c r="O9" t="n">
-        <v>7.598233626762835</v>
+        <v>7.692051580442332</v>
       </c>
       <c r="P9" t="n">
-        <v>395.2480423037872</v>
+        <v>395.107185542503</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35341,28 +35579,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.44269059793371</v>
+        <v>-1.431424160791172</v>
       </c>
       <c r="J10" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6473528324248062</v>
+        <v>0.6453387337307726</v>
       </c>
       <c r="M10" t="n">
-        <v>6.40083713893592</v>
+        <v>6.415772359927415</v>
       </c>
       <c r="N10" t="n">
-        <v>70.48584750683463</v>
+        <v>70.54689771981852</v>
       </c>
       <c r="O10" t="n">
-        <v>8.395585000870078</v>
+        <v>8.399220066162007</v>
       </c>
       <c r="P10" t="n">
-        <v>395.3379370568506</v>
+        <v>395.2279166437007</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35419,28 +35657,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.301382961477539</v>
+        <v>-1.283083259020632</v>
       </c>
       <c r="J11" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K11" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6216780675944913</v>
+        <v>0.613181163726926</v>
       </c>
       <c r="M11" t="n">
-        <v>6.360181482614475</v>
+        <v>6.413954738482182</v>
       </c>
       <c r="N11" t="n">
-        <v>64.0711297152459</v>
+        <v>65.06443936505312</v>
       </c>
       <c r="O11" t="n">
-        <v>8.00444437267484</v>
+        <v>8.066253118087301</v>
       </c>
       <c r="P11" t="n">
-        <v>391.9823340094139</v>
+        <v>391.8036230536001</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35497,28 +35735,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.115743400316617</v>
+        <v>-1.093577877889102</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K12" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4634152926591653</v>
+        <v>0.4512900950176311</v>
       </c>
       <c r="M12" t="n">
-        <v>7.235387548817465</v>
+        <v>7.290714114701101</v>
       </c>
       <c r="N12" t="n">
-        <v>89.24835860016567</v>
+        <v>90.72496749720692</v>
       </c>
       <c r="O12" t="n">
-        <v>9.447134941354742</v>
+        <v>9.524965485355153</v>
       </c>
       <c r="P12" t="n">
-        <v>386.7936885704738</v>
+        <v>386.5759952189938</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35575,28 +35813,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.202312173712573</v>
+        <v>-1.181450907729968</v>
       </c>
       <c r="J13" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K13" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5182092634564798</v>
+        <v>0.507583170611198</v>
       </c>
       <c r="M13" t="n">
-        <v>6.785772915558724</v>
+        <v>6.838667030630075</v>
       </c>
       <c r="N13" t="n">
-        <v>83.04989202364125</v>
+        <v>84.32028207910487</v>
       </c>
       <c r="O13" t="n">
-        <v>9.113171348309065</v>
+        <v>9.182607586034855</v>
       </c>
       <c r="P13" t="n">
-        <v>388.5812354170237</v>
+        <v>388.3756451548249</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35653,28 +35891,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9574571972696908</v>
+        <v>-0.9448212995646197</v>
       </c>
       <c r="J14" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K14" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L14" t="n">
-        <v>0.316275399065738</v>
+        <v>0.3124983569652998</v>
       </c>
       <c r="M14" t="n">
-        <v>8.501185573045507</v>
+        <v>8.495852732466719</v>
       </c>
       <c r="N14" t="n">
-        <v>122.6755416222991</v>
+        <v>122.5071547070997</v>
       </c>
       <c r="O14" t="n">
-        <v>11.07589913380846</v>
+        <v>11.06829502259041</v>
       </c>
       <c r="P14" t="n">
-        <v>383.716300542425</v>
+        <v>383.5920572082575</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35731,28 +35969,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.113765776968873</v>
+        <v>-1.102983447139037</v>
       </c>
       <c r="J15" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K15" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4496279818021095</v>
+        <v>0.4471327320312132</v>
       </c>
       <c r="M15" t="n">
-        <v>7.809775505231473</v>
+        <v>7.814032097098323</v>
       </c>
       <c r="N15" t="n">
-        <v>94.52032604422961</v>
+        <v>94.36486093882966</v>
       </c>
       <c r="O15" t="n">
-        <v>9.722156450306157</v>
+        <v>9.714157757563425</v>
       </c>
       <c r="P15" t="n">
-        <v>388.3626398791878</v>
+        <v>388.2572471856957</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35809,28 +36047,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8734099440887821</v>
+        <v>-0.8566274245070783</v>
       </c>
       <c r="J16" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K16" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2399107510726198</v>
+        <v>0.234087079299083</v>
       </c>
       <c r="M16" t="n">
-        <v>8.377800187502693</v>
+        <v>8.394200151227256</v>
       </c>
       <c r="N16" t="n">
-        <v>149.7256618992632</v>
+        <v>149.9005201664668</v>
       </c>
       <c r="O16" t="n">
-        <v>12.23624378227498</v>
+        <v>12.2433867931413</v>
       </c>
       <c r="P16" t="n">
-        <v>385.9496199118446</v>
+        <v>385.7853501601477</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35887,28 +36125,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.13007866346054</v>
+        <v>-1.110117273606559</v>
       </c>
       <c r="J17" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K17" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2932237015272759</v>
+        <v>0.2870337776194019</v>
       </c>
       <c r="M17" t="n">
-        <v>8.689014800001479</v>
+        <v>8.749910569119645</v>
       </c>
       <c r="N17" t="n">
-        <v>192.9963285814445</v>
+        <v>193.3920820919083</v>
       </c>
       <c r="O17" t="n">
-        <v>13.8923118515762</v>
+        <v>13.90654817314161</v>
       </c>
       <c r="P17" t="n">
-        <v>398.0919523008319</v>
+        <v>397.8978215451635</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35965,28 +36203,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9372548857688155</v>
+        <v>-0.9215406272889918</v>
       </c>
       <c r="J18" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K18" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3601350885431766</v>
+        <v>0.3532027620604964</v>
       </c>
       <c r="M18" t="n">
-        <v>7.708582418185054</v>
+        <v>7.725815364425984</v>
       </c>
       <c r="N18" t="n">
-        <v>97.61823557937376</v>
+        <v>98.01216533062265</v>
       </c>
       <c r="O18" t="n">
-        <v>9.880194106361158</v>
+        <v>9.900109359528441</v>
       </c>
       <c r="P18" t="n">
-        <v>405.1294546150912</v>
+        <v>404.976288778835</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36043,28 +36281,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.049977546381093</v>
+        <v>-1.040976690463972</v>
       </c>
       <c r="J19" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K19" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4305157691522268</v>
+        <v>0.4289257507834162</v>
       </c>
       <c r="M19" t="n">
-        <v>7.342331781648196</v>
+        <v>7.345358073348182</v>
       </c>
       <c r="N19" t="n">
-        <v>90.89949779144659</v>
+        <v>90.62852250377007</v>
       </c>
       <c r="O19" t="n">
-        <v>9.534122811850422</v>
+        <v>9.519901391494036</v>
       </c>
       <c r="P19" t="n">
-        <v>404.2356070843259</v>
+        <v>404.1479710832547</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36102,7 +36340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T439"/>
+  <dimension ref="A1:T442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80671,6 +80909,312 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-40.97518902680337,172.10354994702357</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-40.974527727316,172.10334678637878</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-40.97385544501368,172.10322156434927</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-40.97318106616526,172.1031111810332</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-40.97251510600585,172.10294097128167</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-40.97184500876547,172.10280008962806</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-40.971173111191675,172.1026719433689</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-40.97050566639376,172.10251213190426</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-40.969844138821806,172.10231025727748</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-40.969187014453716,172.1020770700362</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-40.96852573736021,172.10186262044596</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-40.96785369640188,172.1017260162633</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-40.96717848336459,172.10162539131716</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-40.96650963996665,172.10147592897457</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-40.96585502458748,172.10121683440775</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-40.96519907911565,172.10096793187336</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>-40.96454458659966,172.10070778701194</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>-40.963863032852466,172.10065600931568</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-40.97518902680337,172.10354994702357</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-40.974527727316,172.10334678637878</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-40.97385544501368,172.10322156434927</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-40.97318106616526,172.1031111810332</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-40.97251510600585,172.10294097128167</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-40.97184500876547,172.10280008962806</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-40.971173111191675,172.1026719433689</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-40.97050566639376,172.10251213190426</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-40.969844007179084,172.10231119200986</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-40.96918808403965,172.1020694754084</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-40.96852511930301,172.10186718287454</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-40.96785369640188,172.1017260162633</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-40.96717848336459,172.10162539131716</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-40.96650963996665,172.10147592897457</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-40.96585502458748,172.10121683440775</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-40.96519907911565,172.10096793187336</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>-40.96454458659966,172.10070778701194</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>-40.963863032852466,172.10065600931568</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-40.97518357984602,172.1035886246441</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-40.9745226918027,172.10338254238127</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-40.9738518576356,172.1032470373244</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-40.97317872943946,172.10312777335415</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-40.97250067430818,172.10304344536183</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-40.9718434783914,172.10281095621428</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-40.97117291372486,172.10267334549505</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-40.97054654142817,172.10222189450036</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-40.96984379325965,172.10231271094997</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-40.969188742246125,172.10206480179116</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-40.96852439031226,172.10187256420045</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-40.96785281341712,172.10173280970167</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-40.967177966282,172.1016293737566</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-40.96650789102026,172.101489398856</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-40.96585412731387,172.10122374497672</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>-40.96519882058243,172.1009699230352</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>-40.96454448014621,172.10070860689433</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>-40.96386198352448,172.1006640909297</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0331/nzd0331.xlsx
+++ b/data/nzd0331/nzd0331.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29486,7 +29486,7 @@
         <v>368.83</v>
       </c>
       <c r="F442" t="n">
-        <v>361.47</v>
+        <v>369.12</v>
       </c>
       <c r="G442" t="n">
         <v>366.79</v>
@@ -29495,16 +29495,16 @@
         <v>363.99</v>
       </c>
       <c r="I442" t="n">
-        <v>388.05</v>
+        <v>362.68</v>
       </c>
       <c r="J442" t="n">
-        <v>365.7</v>
+        <v>378.29</v>
       </c>
       <c r="K442" t="n">
         <v>372.34</v>
       </c>
       <c r="L442" t="n">
-        <v>374.19</v>
+        <v>385.25</v>
       </c>
       <c r="M442" t="n">
         <v>372.59</v>
@@ -29528,6 +29528,204 @@
         <v>382.95</v>
       </c>
       <c r="T442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="C443" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="D443" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="E443" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="F443" t="n">
+        <v>369.14</v>
+      </c>
+      <c r="G443" t="n">
+        <v>369.42</v>
+      </c>
+      <c r="H443" t="n">
+        <v>365.56</v>
+      </c>
+      <c r="I443" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="J443" t="n">
+        <v>380.76</v>
+      </c>
+      <c r="K443" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="L443" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="M443" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="N443" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="O443" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="P443" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="R443" t="n">
+        <v>394</v>
+      </c>
+      <c r="S443" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="C444" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="D444" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="E444" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="F444" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="G444" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="H444" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="I444" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="J444" t="n">
+        <v>380.76</v>
+      </c>
+      <c r="K444" t="n">
+        <v>373.97</v>
+      </c>
+      <c r="L444" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="M444" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="N444" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="O444" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="P444" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="R444" t="n">
+        <v>394</v>
+      </c>
+      <c r="S444" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>389.19</v>
+      </c>
+      <c r="C445" t="n">
+        <v>391.25</v>
+      </c>
+      <c r="D445" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="E445" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="F445" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="G445" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="H445" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="I445" t="n">
+        <v>381.96</v>
+      </c>
+      <c r="J445" t="n">
+        <v>393.89</v>
+      </c>
+      <c r="K445" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="L445" t="n">
+        <v>401.41</v>
+      </c>
+      <c r="M445" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="N445" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="O445" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="P445" t="n">
+        <v>381.01</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="R445" t="n">
+        <v>395.19</v>
+      </c>
+      <c r="S445" t="n">
+        <v>387.07</v>
+      </c>
+      <c r="T445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29544,7 +29742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34787,6 +34985,36 @@
       </c>
       <c r="B524" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -34955,28 +35183,28 @@
         <v>0.0999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.507784085173973</v>
+        <v>-1.499931785386508</v>
       </c>
       <c r="J2" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5859872302884308</v>
+        <v>0.585240613668778</v>
       </c>
       <c r="M2" t="n">
-        <v>7.866338808770673</v>
+        <v>7.851474824051518</v>
       </c>
       <c r="N2" t="n">
-        <v>100.2815720158498</v>
+        <v>100.3161904734812</v>
       </c>
       <c r="O2" t="n">
-        <v>10.01406870437036</v>
+        <v>10.01579704634041</v>
       </c>
       <c r="P2" t="n">
-        <v>411.8403816067302</v>
+        <v>411.7629959992271</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35033,28 +35261,28 @@
         <v>0.0688</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.223810631281719</v>
+        <v>-1.214233309245475</v>
       </c>
       <c r="J3" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5296277397333835</v>
+        <v>0.526997347217224</v>
       </c>
       <c r="M3" t="n">
-        <v>7.188298970677899</v>
+        <v>7.192596022447336</v>
       </c>
       <c r="N3" t="n">
-        <v>83.69467242559725</v>
+        <v>83.90452706388717</v>
       </c>
       <c r="O3" t="n">
-        <v>9.148479241141516</v>
+        <v>9.159941433431065</v>
       </c>
       <c r="P3" t="n">
-        <v>405.7924690724522</v>
+        <v>405.6986366611893</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35111,28 +35339,28 @@
         <v>0.0873</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.213209416094739</v>
+        <v>-1.203974267686136</v>
       </c>
       <c r="J4" t="n">
+        <v>444</v>
+      </c>
+      <c r="K4" t="n">
         <v>441</v>
       </c>
-      <c r="K4" t="n">
-        <v>438</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6357308852924384</v>
+        <v>0.6335976694192129</v>
       </c>
       <c r="M4" t="n">
-        <v>5.794757720451288</v>
+        <v>5.805008289001103</v>
       </c>
       <c r="N4" t="n">
-        <v>52.89958463144672</v>
+        <v>52.98125986542657</v>
       </c>
       <c r="O4" t="n">
-        <v>7.273210063750855</v>
+        <v>7.278822697760028</v>
       </c>
       <c r="P4" t="n">
-        <v>402.8024630008031</v>
+        <v>402.7116260010972</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35189,28 +35417,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.384311315993423</v>
+        <v>-1.378018873530186</v>
       </c>
       <c r="J5" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6634595256732159</v>
+        <v>0.6640239886506355</v>
       </c>
       <c r="M5" t="n">
-        <v>6.012559521503573</v>
+        <v>6.010806932270519</v>
       </c>
       <c r="N5" t="n">
-        <v>60.59206886830842</v>
+        <v>60.35043269459729</v>
       </c>
       <c r="O5" t="n">
-        <v>7.784090754115629</v>
+        <v>7.768554092918276</v>
       </c>
       <c r="P5" t="n">
-        <v>399.3282295688964</v>
+        <v>399.2660329139138</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35267,28 +35495,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.461007929357957</v>
+        <v>-1.446414443450678</v>
       </c>
       <c r="J6" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6729669464565554</v>
+        <v>0.669076959310571</v>
       </c>
       <c r="M6" t="n">
-        <v>6.153063195109411</v>
+        <v>6.201813170088722</v>
       </c>
       <c r="N6" t="n">
-        <v>64.69951065087035</v>
+        <v>65.03313601984328</v>
       </c>
       <c r="O6" t="n">
-        <v>8.043600602396314</v>
+        <v>8.064312495175475</v>
       </c>
       <c r="P6" t="n">
-        <v>398.1593647121544</v>
+        <v>398.0150757366983</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35345,28 +35573,28 @@
         <v>0.1061</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.432988012196715</v>
+        <v>-1.421764319385228</v>
       </c>
       <c r="J7" t="n">
+        <v>444</v>
+      </c>
+      <c r="K7" t="n">
         <v>441</v>
       </c>
-      <c r="K7" t="n">
-        <v>438</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.6314379283705958</v>
+        <v>0.6294274748670265</v>
       </c>
       <c r="M7" t="n">
-        <v>6.545852121187799</v>
+        <v>6.559538406225435</v>
       </c>
       <c r="N7" t="n">
-        <v>75.1133907973058</v>
+        <v>75.15534377512677</v>
       </c>
       <c r="O7" t="n">
-        <v>8.66679818602613</v>
+        <v>8.66921817554079</v>
       </c>
       <c r="P7" t="n">
-        <v>397.3151744519298</v>
+        <v>397.2048163154476</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35423,28 +35651,28 @@
         <v>0.0926</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.461675678353924</v>
+        <v>-1.454946769394087</v>
       </c>
       <c r="J8" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K8" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7134952359665163</v>
+        <v>0.7137681587714088</v>
       </c>
       <c r="M8" t="n">
-        <v>5.681980314094001</v>
+        <v>5.672963134204846</v>
       </c>
       <c r="N8" t="n">
-        <v>54.00425020413695</v>
+        <v>53.84800887734553</v>
       </c>
       <c r="O8" t="n">
-        <v>7.348758412421581</v>
+        <v>7.338120255034359</v>
       </c>
       <c r="P8" t="n">
-        <v>397.3921371513079</v>
+        <v>397.3263012671615</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35501,28 +35729,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.307856256843581</v>
+        <v>-1.305733530325711</v>
       </c>
       <c r="J9" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K9" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6448822725871937</v>
+        <v>0.6496927998497035</v>
       </c>
       <c r="M9" t="n">
-        <v>5.975761990487921</v>
+        <v>5.944378482506411</v>
       </c>
       <c r="N9" t="n">
-        <v>59.16765751618538</v>
+        <v>58.19197057720135</v>
       </c>
       <c r="O9" t="n">
-        <v>7.692051580442332</v>
+        <v>7.628366180067744</v>
       </c>
       <c r="P9" t="n">
-        <v>395.107185542503</v>
+        <v>395.0858975066436</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35579,28 +35807,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.431424160791172</v>
+        <v>-1.391218500850652</v>
       </c>
       <c r="J10" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K10" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6453387337307726</v>
+        <v>0.6150883901333308</v>
       </c>
       <c r="M10" t="n">
-        <v>6.415772359927415</v>
+        <v>6.584764937982337</v>
       </c>
       <c r="N10" t="n">
-        <v>70.54689771981852</v>
+        <v>76.46548717123946</v>
       </c>
       <c r="O10" t="n">
-        <v>8.399220066162007</v>
+        <v>8.74445465259209</v>
       </c>
       <c r="P10" t="n">
-        <v>395.2279166437007</v>
+        <v>394.8331246821076</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35657,28 +35885,28 @@
         <v>0.0755</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.283083259020632</v>
+        <v>-1.256987589637054</v>
       </c>
       <c r="J11" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K11" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L11" t="n">
-        <v>0.613181163726926</v>
+        <v>0.595189037221411</v>
       </c>
       <c r="M11" t="n">
-        <v>6.413954738482182</v>
+        <v>6.507957234812961</v>
       </c>
       <c r="N11" t="n">
-        <v>65.06443936505312</v>
+        <v>67.84386974769689</v>
       </c>
       <c r="O11" t="n">
-        <v>8.066253118087301</v>
+        <v>8.236739023891486</v>
       </c>
       <c r="P11" t="n">
-        <v>391.8036230536001</v>
+        <v>391.5472239857006</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35735,28 +35963,28 @@
         <v>0.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.093577877889102</v>
+        <v>-1.038598304821002</v>
       </c>
       <c r="J12" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K12" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4512900950176311</v>
+        <v>0.39889419990119</v>
       </c>
       <c r="M12" t="n">
-        <v>7.290714114701101</v>
+        <v>7.527088117745041</v>
       </c>
       <c r="N12" t="n">
-        <v>90.72496749720692</v>
+        <v>102.198159739794</v>
       </c>
       <c r="O12" t="n">
-        <v>9.524965485355153</v>
+        <v>10.1093105472032</v>
       </c>
       <c r="P12" t="n">
-        <v>386.5759952189938</v>
+        <v>386.0329766657513</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35813,28 +36041,28 @@
         <v>0.0873</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.181450907729968</v>
+        <v>-1.156599804002711</v>
       </c>
       <c r="J13" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K13" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L13" t="n">
-        <v>0.507583170611198</v>
+        <v>0.49266358389762</v>
       </c>
       <c r="M13" t="n">
-        <v>6.838667030630075</v>
+        <v>6.914224255140287</v>
       </c>
       <c r="N13" t="n">
-        <v>84.32028207910487</v>
+        <v>86.43469499746477</v>
       </c>
       <c r="O13" t="n">
-        <v>9.182607586034855</v>
+        <v>9.297026137290612</v>
       </c>
       <c r="P13" t="n">
-        <v>388.3756451548249</v>
+        <v>388.129252916782</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35891,28 +36119,28 @@
         <v>0.1585</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9448212995646197</v>
+        <v>-0.9294302606569022</v>
       </c>
       <c r="J14" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K14" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3124983569652998</v>
+        <v>0.3067505291571374</v>
       </c>
       <c r="M14" t="n">
-        <v>8.495852732466719</v>
+        <v>8.502411965650259</v>
       </c>
       <c r="N14" t="n">
-        <v>122.5071547070997</v>
+        <v>122.7111242232248</v>
       </c>
       <c r="O14" t="n">
-        <v>11.06829502259041</v>
+        <v>11.07750532490167</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5920572082575</v>
+        <v>383.439805452215</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35969,28 +36197,28 @@
         <v>0.0861</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.102983447139037</v>
+        <v>-1.090742729108357</v>
       </c>
       <c r="J15" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K15" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4471327320312132</v>
+        <v>0.443499704913759</v>
       </c>
       <c r="M15" t="n">
-        <v>7.814032097098323</v>
+        <v>7.825983603514304</v>
       </c>
       <c r="N15" t="n">
-        <v>94.36486093882966</v>
+        <v>94.37008926827438</v>
       </c>
       <c r="O15" t="n">
-        <v>9.714157757563425</v>
+        <v>9.714426862572717</v>
       </c>
       <c r="P15" t="n">
-        <v>388.2572471856957</v>
+        <v>388.1368697080467</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36047,28 +36275,28 @@
         <v>0.0731</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8566274245070783</v>
+        <v>-0.8376756300819909</v>
       </c>
       <c r="J16" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K16" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L16" t="n">
-        <v>0.234087079299083</v>
+        <v>0.2268576495642175</v>
       </c>
       <c r="M16" t="n">
-        <v>8.394200151227256</v>
+        <v>8.425338509192136</v>
       </c>
       <c r="N16" t="n">
-        <v>149.9005201664668</v>
+        <v>150.4610351703252</v>
       </c>
       <c r="O16" t="n">
-        <v>12.2433867931413</v>
+        <v>12.26625595568286</v>
       </c>
       <c r="P16" t="n">
-        <v>385.7853501601477</v>
+        <v>385.5987306311195</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36125,28 +36353,28 @@
         <v>0.0936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.110117273606559</v>
+        <v>-1.087505667301719</v>
       </c>
       <c r="J17" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K17" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2870337776194019</v>
+        <v>0.2792318651277099</v>
       </c>
       <c r="M17" t="n">
-        <v>8.749910569119645</v>
+        <v>8.829259306874619</v>
       </c>
       <c r="N17" t="n">
-        <v>193.3920820919083</v>
+        <v>194.3355522802778</v>
       </c>
       <c r="O17" t="n">
-        <v>13.90654817314161</v>
+        <v>13.94042869786571</v>
       </c>
       <c r="P17" t="n">
-        <v>397.8978215451635</v>
+        <v>397.676578487192</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36203,28 +36431,28 @@
         <v>0.0752</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9215406272889918</v>
+        <v>-0.9040566380522064</v>
       </c>
       <c r="J18" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K18" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3532027620604964</v>
+        <v>0.3446735412581468</v>
       </c>
       <c r="M18" t="n">
-        <v>7.725815364425984</v>
+        <v>7.753428056579322</v>
       </c>
       <c r="N18" t="n">
-        <v>98.01216533062265</v>
+        <v>98.68242903019919</v>
       </c>
       <c r="O18" t="n">
-        <v>9.900109359528441</v>
+        <v>9.933903010911632</v>
       </c>
       <c r="P18" t="n">
-        <v>404.976288778835</v>
+        <v>404.8048463039261</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36281,28 +36509,28 @@
         <v>0.1483</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.040976690463972</v>
+        <v>-1.029740441729522</v>
       </c>
       <c r="J19" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K19" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4289257507834162</v>
+        <v>0.4256415671177635</v>
       </c>
       <c r="M19" t="n">
-        <v>7.345358073348182</v>
+        <v>7.360691756291632</v>
       </c>
       <c r="N19" t="n">
-        <v>90.62852250377007</v>
+        <v>90.57481341356082</v>
       </c>
       <c r="O19" t="n">
-        <v>9.519901391494036</v>
+        <v>9.517080088638574</v>
       </c>
       <c r="P19" t="n">
-        <v>404.1479710832547</v>
+        <v>404.0379051994452</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36340,7 +36568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T442"/>
+  <dimension ref="A1:T445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81141,7 +81369,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>-40.97250067430818,172.10304344536183</t>
+          <t>-40.972513262966324,172.1029540580537</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -81156,12 +81384,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>-40.97054654142817,172.10222189450036</t>
+          <t>-40.97050479425338,172.10251832456652</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>-40.96984379325965,172.10231271094997</t>
+          <t>-40.96986451044127,172.10216560739758</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
@@ -81171,7 +81399,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>-40.96852439031226,172.10187256420045</t>
+          <t>-40.96854191771573,172.10174317837644</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -81210,6 +81438,312 @@
         </is>
       </c>
       <c r="T442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-40.975181670939435,172.10360217933743</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-40.97452147406253,172.10339118925688</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-40.97385175890036,172.1032477384154</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-40.973177067400634,172.10313957493386</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-40.972513295877754,172.10295382436135</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-40.97184780622077,172.1027802259746</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-40.9711754972479,172.1026550010111</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-40.970507295485284,172.1025005644781</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-40.96986857487017,172.10213674751628</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-40.969191424435536,172.10204575679995</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-40.96855885862066,172.1016181209486</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-40.96785628445834,172.10170610446025</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-40.96717998898665,172.10161379539025</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-40.966510141837944,172.1014720637041</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-40.96585563290833,172.1012121492761</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>-40.96520087363937,172.1009541108672</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>-40.964546563591206,172.1006925606249</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>-40.96386426467154,172.10064652220328</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-40.975181670939435,172.10360217933743</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-40.97452147406253,172.10339118925688</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-40.97386301469198,172.1031678140261</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-40.97317563574244,172.10314974065057</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-40.97251081106321,172.1029714681333</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-40.97184408725002,172.10280663294887</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-40.97117072513296,172.10268888572557</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-40.970507295485284,172.1025005644781</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-40.96986857487017,172.10213674751628</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-40.969191424435536,172.10204575679995</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-40.96855885862066,172.1016181209486</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-40.96785628445834,172.10170610446025</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-40.96717998898665,172.10161379539025</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-40.966510141837944,172.1014720637041</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-40.96585563290833,172.1012121492761</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>-40.96520087363937,172.1009541108672</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>-40.964546563591206,172.1006925606249</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>-40.96386426467154,172.10064652220328</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-40.97521002461966,172.10340084532322</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-40.97454749077514,172.10320644986092</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-40.97386301469198,172.1031678140261</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-40.97317563574244,172.10314974065057</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-40.97251081106321,172.1029714681333</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-40.97184408725002,172.10280663294887</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-40.97117072513296,172.10268888572557</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-40.9705365202015,172.10229305177023</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-40.96989018039655,172.10198333440573</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-40.96921357294623,172.10188848951523</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-40.96856752711327,172.10155412989292</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-40.967863942040466,172.10164718894</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-40.967185935421966,172.1015679973306</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-40.966512848898965,172.10145121466863</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-40.96586233963301,172.1011604956946</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>-40.96520669822604,172.10090925115585</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>-40.96454837329709,172.10067862262363</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>-40.96386824906864,172.10061583549168</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
